--- a/Gear_Test_Protocol.xlsx
+++ b/Gear_Test_Protocol.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenni\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenni\HES-SO cours\Summer_school\SS2\DSS2_IT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43D3503-A8A4-4008-8373-602D022A0AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DB60E0-20C8-4617-B7DE-DE5E0496BBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="Test Protocol" sheetId="1" r:id="rId1"/>
     <sheet name="Test Setup" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t>Category</t>
   </si>
@@ -140,15 +153,6 @@
     <t>E_GEAR_ERROR is generated and GEARERROR is entered.</t>
   </si>
   <si>
-    <t>Invalid position</t>
-  </si>
-  <si>
-    <t>Simulate an impossible ADC position.</t>
-  </si>
-  <si>
-    <t>Invalid feedback is detected and an error is generated.</t>
-  </si>
-  <si>
     <t>Error recovery</t>
   </si>
   <si>
@@ -309,6 +313,12 @@
   </si>
   <si>
     <t xml:space="preserve">Gear moves to whatever gear requested and every function works well </t>
+  </si>
+  <si>
+    <t xml:space="preserve">entered after multiple attempts </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tries to return to old gear </t>
   </si>
 </sst>
 </file>
@@ -353,7 +363,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -427,13 +437,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <fgColor rgb="FFFEF0F4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <fgColor theme="0"/>
         </patternFill>
       </fill>
@@ -447,6 +450,13 @@
       <border>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FFFEF0F4"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -468,11 +478,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Style de tableau 1" pivot="0" count="5" xr9:uid="{137D0900-64DA-4138-AFDD-5AA1B590F2A5}">
+    <tableStyle name="Style de tableau 1" pivot="0" count="4" xr9:uid="{137D0900-64DA-4138-AFDD-5AA1B590F2A5}">
       <tableStyleElement type="headerRow" dxfId="10"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="9"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="8"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="7"/>
     </tableStyle>
     <tableStyle name="tableau 2" pivot="0" count="7" xr9:uid="{48351426-63DC-4B5B-8A14-442DC14C5C83}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
@@ -503,8 +513,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EEB2F803-74E3-489E-A772-7484556157CB}" name="Tableau1" displayName="Tableau1" ref="A1:F22" totalsRowShown="0">
-  <autoFilter ref="A1:F22" xr:uid="{EEB2F803-74E3-489E-A772-7484556157CB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EEB2F803-74E3-489E-A772-7484556157CB}" name="Tableau1" displayName="Tableau1" ref="A1:F21" totalsRowShown="0">
+  <autoFilter ref="A1:F21" xr:uid="{EEB2F803-74E3-489E-A772-7484556157CB}"/>
   <tableColumns count="6">
     <tableColumn id="2" xr3:uid="{1697032F-354E-49CA-8351-EB4DAD24AE88}" name="Category"/>
     <tableColumn id="3" xr3:uid="{74DDFFDC-F9D9-4FC5-8602-7CC9E6E1B2FE}" name="Test"/>
@@ -802,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -821,13 +831,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -841,16 +851,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -861,13 +871,13 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -885,7 +895,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -894,19 +904,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -923,7 +933,7 @@
         <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -935,16 +945,16 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -955,13 +965,13 @@
         <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -976,10 +986,10 @@
         <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -988,16 +998,16 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -1015,10 +1025,10 @@
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1029,13 +1039,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -1069,7 +1079,7 @@
         <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2"/>
     </row>
@@ -1086,8 +1096,12 @@
       <c r="D15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
@@ -1102,10 +1116,14 @@
       <c r="D16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>35</v>
       </c>
@@ -1118,72 +1136,64 @@
       <c r="D17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1204,42 +1214,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1247,23 +1257,23 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Gear_Test_Protocol.xlsx
+++ b/Gear_Test_Protocol.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenni\HES-SO cours\Summer_school\SS2\DSS2_IT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DB60E0-20C8-4617-B7DE-DE5E0496BBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0AF895-6AF3-4F14-AF9F-1133A6AEB6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="96">
   <si>
     <t>Category</t>
   </si>
@@ -255,9 +255,6 @@
     <t xml:space="preserve">Check the plausability of the adc feedback </t>
   </si>
   <si>
-    <t>ADC value moves slightly and is between 0-4000.</t>
-  </si>
-  <si>
     <t xml:space="preserve">yes </t>
   </si>
   <si>
@@ -319,6 +316,12 @@
   </si>
   <si>
     <t xml:space="preserve">tries to return to old gear </t>
+  </si>
+  <si>
+    <t>ADC value moves, adc is read correctly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adc interrupt stopped working, function is now not interrupt and works </t>
   </si>
 </sst>
 </file>
@@ -863,7 +866,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -874,12 +877,14 @@
         <v>72</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -895,7 +900,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -904,19 +909,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -945,7 +950,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>19</v>
@@ -954,7 +959,7 @@
         <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -965,7 +970,7 @@
         <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>21</v>
@@ -986,10 +991,10 @@
         <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -998,16 +1003,16 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -1028,7 +1033,7 @@
         <v>70</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1039,10 +1044,10 @@
         <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>70</v>
@@ -1097,10 +1102,10 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1117,10 +1122,10 @@
         <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1170,7 +1175,7 @@
         <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>70</v>
@@ -1179,19 +1184,19 @@
     </row>
     <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F20" s="2"/>
     </row>
